--- a/data/trans_dic/P13_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,06</t>
+          <t>0,96; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,71</t>
+          <t>3,54; 7,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,59</t>
+          <t>2,47; 5,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,33</t>
+          <t>4,56; 8,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,47</t>
+          <t>1,1; 3,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,76</t>
+          <t>8,87; 13,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,98</t>
+          <t>4,69; 8,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,48</t>
+          <t>5,76; 8,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,75</t>
+          <t>1,29; 2,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,68</t>
+          <t>6,43; 9,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,54</t>
+          <t>4,05; 6,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,8</t>
+          <t>5,51; 7,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,35</t>
+          <t>2,83; 5,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,51</t>
+          <t>3,66; 6,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,8</t>
+          <t>1,79; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,57</t>
+          <t>1,57; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,73</t>
+          <t>3,19; 6,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,9</t>
+          <t>6,52; 10,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,91</t>
+          <t>3,15; 5,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,71</t>
+          <t>6,13; 8,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,23</t>
+          <t>3,36; 5,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,73</t>
+          <t>5,43; 7,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,46</t>
+          <t>2,8; 4,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,0</t>
+          <t>3,19; 5,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,15</t>
+          <t>2,05; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,85</t>
+          <t>2,68; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,26</t>
+          <t>2,4; 5,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,03</t>
+          <t>3,74; 7,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,27</t>
+          <t>3,9; 7,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,97</t>
+          <t>6,53; 10,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,96</t>
+          <t>3,59; 6,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,29</t>
+          <t>2,46; 7,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,76</t>
+          <t>3,31; 5,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,69</t>
+          <t>5,12; 7,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,64</t>
+          <t>3,28; 5,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,4</t>
+          <t>3,28; 6,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,65</t>
+          <t>2,22; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,19</t>
+          <t>3,51; 6,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,25</t>
+          <t>2,8; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 7,53</t>
+          <t>4,62; 7,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,64</t>
+          <t>5,45; 8,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,91</t>
+          <t>8,3; 12,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,12</t>
+          <t>4,85; 8,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,27</t>
+          <t>6,22; 9,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,12</t>
+          <t>4,18; 6,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,81</t>
+          <t>6,3; 8,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,4</t>
+          <t>4,26; 6,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,06</t>
+          <t>5,9; 8,07</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,83</t>
+          <t>2,63; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,5</t>
+          <t>3,92; 5,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,13</t>
+          <t>2,84; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,67</t>
+          <t>3,76; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,61</t>
+          <t>4,17; 5,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,4</t>
+          <t>8,35; 10,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,33</t>
+          <t>4,8; 6,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,68</t>
+          <t>5,57; 7,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,68</t>
+          <t>6,42; 7,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,1</t>
+          <t>4,03; 5,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,46</t>
+          <t>5,08; 6,46</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6803; 21212</t>
+          <t>6647; 21030</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24309; 47158</t>
+          <t>24834; 50334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17670; 37693</t>
+          <t>16665; 38108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29403; 52789</t>
+          <t>28888; 54339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7512; 23879</t>
+          <t>7574; 23712</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61562; 95772</t>
+          <t>61767; 95438</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32315; 60262</t>
+          <t>31437; 57941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38378; 57070</t>
+          <t>38744; 56358</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17398; 38068</t>
+          <t>17895; 38144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90874; 135405</t>
+          <t>89897; 132709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53985; 87953</t>
+          <t>54445; 88245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73340; 101893</t>
+          <t>71970; 102933</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27762; 51482</t>
+          <t>27251; 51410</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35925; 66234</t>
+          <t>37239; 66175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17599; 38857</t>
+          <t>18262; 39475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20504; 54538</t>
+          <t>18770; 54553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29348; 55486</t>
+          <t>30876; 58143</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68030; 102119</t>
+          <t>67259; 104593</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33622; 61606</t>
+          <t>32848; 61948</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57634; 83371</t>
+          <t>58695; 83880</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64392; 101029</t>
+          <t>64872; 103403</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111037; 158496</t>
+          <t>111256; 156288</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58323; 92021</t>
+          <t>57758; 94109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67661; 129044</t>
+          <t>68651; 128420</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14081; 34961</t>
+          <t>13908; 34230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20562; 44279</t>
+          <t>20277; 42965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18050; 39935</t>
+          <t>18218; 41573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26608; 49508</t>
+          <t>26321; 49582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26310; 49711</t>
+          <t>26670; 49477</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51659; 85122</t>
+          <t>50700; 84080</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29149; 54533</t>
+          <t>28100; 53870</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24384; 67967</t>
+          <t>22979; 66962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46623; 78461</t>
+          <t>45161; 75623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79236; 117803</t>
+          <t>78477; 117719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52682; 86970</t>
+          <t>50603; 85666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54695; 104862</t>
+          <t>53641; 106905</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21291; 43790</t>
+          <t>20871; 43892</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32408; 58637</t>
+          <t>33232; 58480</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24560; 49224</t>
+          <t>26213; 49167</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41860; 69713</t>
+          <t>42777; 71769</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56395; 89734</t>
+          <t>56644; 89044</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86924; 125303</t>
+          <t>87294; 127086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51812; 84664</t>
+          <t>50559; 84720</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66767; 101514</t>
+          <t>68159; 102166</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82475; 121128</t>
+          <t>82716; 123445</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126207; 176135</t>
+          <t>125984; 174840</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83281; 126679</t>
+          <t>84418; 125598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120387; 162861</t>
+          <t>119257; 163004</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85961; 125506</t>
+          <t>86111; 127563</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135106; 188271</t>
+          <t>134333; 185836</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97926; 140090</t>
+          <t>96531; 140779</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124843; 196052</t>
+          <t>130009; 196862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>137011; 189635</t>
+          <t>140887; 192328</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>296176; 369679</t>
+          <t>297009; 369396</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>167866; 223954</t>
+          <t>170000; 226190</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>202910; 280723</t>
+          <t>203776; 280250</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>238296; 303755</t>
+          <t>237495; 301003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>444062; 535778</t>
+          <t>448149; 534402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>280753; 353544</t>
+          <t>279351; 353703</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>365723; 459618</t>
+          <t>361230; 459412</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,03</t>
+          <t>0,96; 2,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,16</t>
+          <t>3,4; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,65</t>
+          <t>2,53; 5,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,58</t>
+          <t>4,61; 8,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,44</t>
+          <t>1,08; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,71</t>
+          <t>8,61; 13,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,64</t>
+          <t>4,66; 8,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,38</t>
+          <t>5,57; 8,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,76</t>
+          <t>1,29; 2,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,49</t>
+          <t>6,59; 9,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,56</t>
+          <t>3,95; 6,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,88</t>
+          <t>5,54; 7,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,35</t>
+          <t>2,97; 5,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,5</t>
+          <t>3,43; 6,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,86</t>
+          <t>1,82; 3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,57</t>
+          <t>2,76; 5,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,0</t>
+          <t>3,07; 5,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,14</t>
+          <t>6,61; 10,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,95</t>
+          <t>3,36; 5,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,77</t>
+          <t>6,02; 8,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,36</t>
+          <t>3,37; 5,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,63</t>
+          <t>5,42; 7,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,56</t>
+          <t>2,77; 4,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,97</t>
+          <t>4,66; 6,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,04</t>
+          <t>2,09; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,68</t>
+          <t>2,62; 5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,47</t>
+          <t>2,35; 5,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,04</t>
+          <t>4,31; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,24</t>
+          <t>3,86; 7,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,83</t>
+          <t>6,76; 10,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,87</t>
+          <t>3,58; 6,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,18</t>
+          <t>5,47; 8,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,55</t>
+          <t>3,41; 5,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,68</t>
+          <t>5,02; 7,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,55</t>
+          <t>3,41; 5,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,53</t>
+          <t>5,32; 7,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,66</t>
+          <t>2,13; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,18</t>
+          <t>3,47; 6,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,24</t>
+          <t>2,78; 5,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,76</t>
+          <t>4,47; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,57</t>
+          <t>5,34; 8,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,08</t>
+          <t>8,13; 12,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,12</t>
+          <t>4,9; 8,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,33</t>
+          <t>7,3; 9,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,23</t>
+          <t>4,15; 6,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,75</t>
+          <t>6,34; 8,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,34</t>
+          <t>4,21; 6,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,07</t>
+          <t>6,3; 8,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,89</t>
+          <t>2,59; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,43</t>
+          <t>3,96; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,15</t>
+          <t>2,85; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,7</t>
+          <t>4,55; 6,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,69</t>
+          <t>4,15; 5,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 10,39</t>
+          <t>8,41; 10,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,39</t>
+          <t>4,77; 6,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,66</t>
+          <t>6,79; 8,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,52</t>
+          <t>3,54; 4,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,66</t>
+          <t>6,35; 7,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,1</t>
+          <t>4,05; 5,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,46</t>
+          <t>5,9; 6,91</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>50297</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86039</t>
+          <t>92071</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6647; 21030</t>
+          <t>6637; 20186</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24834; 50334</t>
+          <t>23855; 47838</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16665; 38108</t>
+          <t>17093; 36544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28888; 54339</t>
+          <t>31713; 57391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7574; 23712</t>
+          <t>7425; 21991</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61767; 95438</t>
+          <t>59960; 94319</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31437; 57941</t>
+          <t>31268; 57145</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38744; 56358</t>
+          <t>40689; 61633</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17895; 38144</t>
+          <t>17764; 38697</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89897; 132709</t>
+          <t>92192; 132423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54445; 88245</t>
+          <t>53121; 85045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71970; 102933</t>
+          <t>78596; 109986</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>115481</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27251; 51410</t>
+          <t>28598; 54719</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37239; 66175</t>
+          <t>34965; 64222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18262; 39475</t>
+          <t>18635; 40364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18770; 54553</t>
+          <t>28927; 53939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30876; 58143</t>
+          <t>29745; 56272</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67259; 104593</t>
+          <t>68181; 104009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32848; 61948</t>
+          <t>35037; 62401</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58695; 83880</t>
+          <t>64392; 92997</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64872; 103403</t>
+          <t>65062; 99884</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111256; 156288</t>
+          <t>111142; 154905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57758; 94109</t>
+          <t>57144; 92099</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68651; 128420</t>
+          <t>98732; 134313</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>55548</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>102658</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13908; 34230</t>
+          <t>14206; 34380</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20277; 42965</t>
+          <t>19809; 43363</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18218; 41573</t>
+          <t>17822; 39397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26321; 49582</t>
+          <t>34629; 64532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26670; 49477</t>
+          <t>26363; 49279</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50700; 84080</t>
+          <t>52479; 84445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28100; 53870</t>
+          <t>28033; 53794</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22979; 66962</t>
+          <t>44416; 70513</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45161; 75623</t>
+          <t>46415; 77384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78477; 117719</t>
+          <t>76913; 118126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50603; 85666</t>
+          <t>52687; 86348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53641; 106905</t>
+          <t>85951; 124396</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>95626</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>152391</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20871; 43892</t>
+          <t>20057; 43559</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33232; 58480</t>
+          <t>32839; 59700</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26213; 49167</t>
+          <t>26068; 49404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42777; 71769</t>
+          <t>44142; 73255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56644; 89044</t>
+          <t>55414; 88139</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87294; 127086</t>
+          <t>85500; 126696</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50559; 84720</t>
+          <t>51142; 85589</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68159; 102166</t>
+          <t>81722; 111570</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82716; 123445</t>
+          <t>82287; 122676</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125984; 174840</t>
+          <t>126642; 176221</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84418; 125598</t>
+          <t>83348; 127573</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>119257; 163004</t>
+          <t>132756; 174290</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86111; 127563</t>
+          <t>84933; 127475</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134333; 185836</t>
+          <t>135453; 190759</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96531; 140779</t>
+          <t>96776; 141560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130009; 196862</t>
+          <t>160618; 213718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>140887; 192328</t>
+          <t>140324; 190043</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>297009; 369396</t>
+          <t>299047; 365052</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>170000; 226190</t>
+          <t>168680; 224144</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>203776; 280250</t>
+          <t>253214; 305625</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>237495; 301003</t>
+          <t>235509; 302413</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>448149; 534402</t>
+          <t>443214; 537191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>279351; 353703</t>
+          <t>281018; 352040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>361230; 459412</t>
+          <t>427953; 501471</t>
         </is>
       </c>
     </row>
